--- a/doc/openclaw_google_trend.xlsx
+++ b/doc/openclaw_google_trend.xlsx
@@ -71,94 +71,94 @@
     <t>qq 开放 平台</t>
   </si>
   <si>
+    <t>相关信息</t>
+  </si>
+  <si>
+    <t>openclaw 更换 模型</t>
+  </si>
+  <si>
+    <t>模型配置</t>
+  </si>
+  <si>
+    <t>arkclaw</t>
+  </si>
+  <si>
+    <t>竞品对比</t>
+  </si>
+  <si>
+    <t>pinchbench</t>
+  </si>
+  <si>
+    <t>周边项目</t>
+  </si>
+  <si>
+    <t>openclaw 图标</t>
+  </si>
+  <si>
+    <t>openclaw 常用 命令</t>
+  </si>
+  <si>
+    <t>maxclaw</t>
+  </si>
+  <si>
+    <t>openclaw101</t>
+  </si>
+  <si>
+    <t>openclaw hub</t>
+  </si>
+  <si>
+    <t>2.5</t>
+  </si>
+  <si>
+    <t>openclaw acp</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>openclaw subagent</t>
+  </si>
+  <si>
+    <t>1.9</t>
+  </si>
+  <si>
+    <t>龙虾</t>
+  </si>
+  <si>
+    <t>概念了解</t>
+  </si>
+  <si>
+    <t>node js</t>
+  </si>
+  <si>
+    <t>1.8</t>
+  </si>
+  <si>
+    <t>龙虾 openclaw</t>
+  </si>
+  <si>
+    <t>小 龙虾</t>
+  </si>
+  <si>
+    <t>openclaw 技能</t>
+  </si>
+  <si>
+    <t>1.5</t>
+  </si>
+  <si>
+    <t>openclaw 安装 skill</t>
+  </si>
+  <si>
+    <t>1.4</t>
+  </si>
+  <si>
+    <t>openclaw 接 入 微信</t>
+  </si>
+  <si>
+    <t>1.3</t>
+  </si>
+  <si>
     <t>渠道接入</t>
-  </si>
-  <si>
-    <t>openclaw 更换 模型</t>
-  </si>
-  <si>
-    <t>模型配置</t>
-  </si>
-  <si>
-    <t>arkclaw</t>
-  </si>
-  <si>
-    <t>竞品对比</t>
-  </si>
-  <si>
-    <t>pinchbench</t>
-  </si>
-  <si>
-    <t>周边项目</t>
-  </si>
-  <si>
-    <t>openclaw 图标</t>
-  </si>
-  <si>
-    <t>相关信息</t>
-  </si>
-  <si>
-    <t>openclaw 常用 命令</t>
-  </si>
-  <si>
-    <t>maxclaw</t>
-  </si>
-  <si>
-    <t>openclaw101</t>
-  </si>
-  <si>
-    <t>openclaw hub</t>
-  </si>
-  <si>
-    <t>2.5</t>
-  </si>
-  <si>
-    <t>openclaw acp</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>openclaw subagent</t>
-  </si>
-  <si>
-    <t>1.9</t>
-  </si>
-  <si>
-    <t>龙虾</t>
-  </si>
-  <si>
-    <t>概念了解</t>
-  </si>
-  <si>
-    <t>node js</t>
-  </si>
-  <si>
-    <t>1.8</t>
-  </si>
-  <si>
-    <t>龙虾 openclaw</t>
-  </si>
-  <si>
-    <t>小 龙虾</t>
-  </si>
-  <si>
-    <t>openclaw 技能</t>
-  </si>
-  <si>
-    <t>1.5</t>
-  </si>
-  <si>
-    <t>openclaw 安装 skill</t>
-  </si>
-  <si>
-    <t>1.4</t>
-  </si>
-  <si>
-    <t>openclaw 接 入 微信</t>
-  </si>
-  <si>
-    <t>1.3</t>
   </si>
   <si>
     <t>openclaw onboard</t>
@@ -681,7 +681,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -692,13 +692,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1172,28 +1165,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1202,118 +1198,115 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1667,7 +1660,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:E189"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="4"/>
   <cols>
@@ -1827,12 +1820,12 @@
         <v>7</v>
       </c>
       <c r="E9" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B10">
         <v>2</v>
@@ -1849,7 +1842,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B11">
         <v>2</v>
@@ -1866,7 +1859,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -1878,18 +1871,18 @@
         <v>7</v>
       </c>
       <c r="E12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" hidden="1" spans="1:5">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B13">
         <v>9</v>
       </c>
       <c r="C13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D13" t="s">
         <v>7</v>
@@ -1898,15 +1891,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" hidden="1" spans="1:5">
       <c r="A14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B14">
         <v>4</v>
       </c>
       <c r="C14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D14" t="s">
         <v>7</v>
@@ -1915,15 +1908,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" hidden="1" spans="1:5">
       <c r="A15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B15">
         <v>3</v>
       </c>
       <c r="C15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D15" t="s">
         <v>7</v>
@@ -1932,32 +1925,32 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" hidden="1" spans="1:5">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B16">
         <v>39</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D16" t="s">
         <v>7</v>
       </c>
       <c r="E16" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" hidden="1" spans="1:5">
+      <c r="A17" t="s">
         <v>32</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" t="s">
-        <v>33</v>
       </c>
       <c r="B17">
         <v>4</v>
       </c>
       <c r="C17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D17" t="s">
         <v>7</v>
@@ -1966,49 +1959,49 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" hidden="1" spans="1:5">
       <c r="A18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B18">
         <v>39</v>
       </c>
       <c r="C18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="s">
         <v>7</v>
       </c>
       <c r="E18" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" hidden="1" spans="1:5">
       <c r="A19" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B19">
         <v>11</v>
       </c>
       <c r="C19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D19" t="s">
         <v>7</v>
       </c>
       <c r="E19" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" hidden="1" spans="1:5">
       <c r="A20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B20">
         <v>13</v>
       </c>
       <c r="C20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D20" t="s">
         <v>7</v>
@@ -2017,15 +2010,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" hidden="1" spans="1:5">
       <c r="A21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B21">
         <v>9</v>
       </c>
       <c r="C21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D21" t="s">
         <v>7</v>
@@ -2034,24 +2027,24 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" hidden="1" spans="1:5">
       <c r="A22" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B22">
         <v>9</v>
       </c>
       <c r="C22" t="s">
+        <v>41</v>
+      </c>
+      <c r="D22" t="s">
+        <v>7</v>
+      </c>
+      <c r="E22" t="s">
         <v>42</v>
       </c>
-      <c r="D22" t="s">
-        <v>7</v>
-      </c>
-      <c r="E22" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
+    </row>
+    <row r="23" hidden="1" spans="1:5">
       <c r="A23" t="s">
         <v>43</v>
       </c>
@@ -2059,7 +2052,7 @@
         <v>4</v>
       </c>
       <c r="C23" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D23" t="s">
         <v>7</v>
@@ -2068,7 +2061,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" hidden="1" spans="1:5">
       <c r="A24" t="s">
         <v>44</v>
       </c>
@@ -2082,10 +2075,10 @@
         <v>7</v>
       </c>
       <c r="E24" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" hidden="1" spans="1:5">
       <c r="A25" t="s">
         <v>46</v>
       </c>
@@ -2102,7 +2095,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" hidden="1" spans="1:5">
       <c r="A26" t="s">
         <v>48</v>
       </c>
@@ -2119,7 +2112,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" hidden="1" spans="1:5">
       <c r="A27" t="s">
         <v>50</v>
       </c>
@@ -2136,7 +2129,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" hidden="1" spans="1:5">
       <c r="A28" t="s">
         <v>52</v>
       </c>
@@ -2150,10 +2143,10 @@
         <v>7</v>
       </c>
       <c r="E28" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="29" hidden="1" spans="1:5">
       <c r="A29" t="s">
         <v>53</v>
       </c>
@@ -2167,10 +2160,10 @@
         <v>7</v>
       </c>
       <c r="E29" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="30" hidden="1" spans="1:5">
       <c r="A30" t="s">
         <v>54</v>
       </c>
@@ -2187,7 +2180,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" hidden="1" spans="1:5">
       <c r="A31" t="s">
         <v>56</v>
       </c>
@@ -2201,10 +2194,10 @@
         <v>7</v>
       </c>
       <c r="E31" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" hidden="1" spans="1:5">
       <c r="A32" t="s">
         <v>57</v>
       </c>
@@ -2221,7 +2214,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" hidden="1" spans="1:5">
       <c r="A33" t="s">
         <v>58</v>
       </c>
@@ -2238,7 +2231,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" hidden="1" spans="1:5">
       <c r="A34" t="s">
         <v>59</v>
       </c>
@@ -2255,7 +2248,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" hidden="1" spans="1:5">
       <c r="A35" t="s">
         <v>60</v>
       </c>
@@ -2269,10 +2262,10 @@
         <v>7</v>
       </c>
       <c r="E35" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="36" hidden="1" spans="1:5">
       <c r="A36" t="s">
         <v>61</v>
       </c>
@@ -2289,7 +2282,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" hidden="1" spans="1:5">
       <c r="A37" t="s">
         <v>62</v>
       </c>
@@ -2306,7 +2299,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" hidden="1" spans="1:5">
       <c r="A38" t="s">
         <v>64</v>
       </c>
@@ -2323,7 +2316,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" hidden="1" spans="1:5">
       <c r="A39" t="s">
         <v>65</v>
       </c>
@@ -2337,10 +2330,10 @@
         <v>7</v>
       </c>
       <c r="E39" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="40" hidden="1" spans="1:5">
       <c r="A40" t="s">
         <v>66</v>
       </c>
@@ -2357,7 +2350,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" hidden="1" spans="1:5">
       <c r="A41" t="s">
         <v>67</v>
       </c>
@@ -2374,7 +2367,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" hidden="1" spans="1:5">
       <c r="A42" t="s">
         <v>68</v>
       </c>
@@ -2388,10 +2381,10 @@
         <v>7</v>
       </c>
       <c r="E42" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="43" hidden="1" spans="1:5">
       <c r="A43" t="s">
         <v>70</v>
       </c>
@@ -2408,7 +2401,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" hidden="1" spans="1:5">
       <c r="A44" t="s">
         <v>71</v>
       </c>
@@ -2425,7 +2418,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" hidden="1" spans="1:5">
       <c r="A45" t="s">
         <v>72</v>
       </c>
@@ -2442,7 +2435,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" hidden="1" spans="1:5">
       <c r="A46" t="s">
         <v>73</v>
       </c>
@@ -2459,7 +2452,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" hidden="1" spans="1:5">
       <c r="A47" t="s">
         <v>74</v>
       </c>
@@ -2473,10 +2466,10 @@
         <v>7</v>
       </c>
       <c r="E47" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="48" hidden="1" spans="1:5">
       <c r="A48" t="s">
         <v>75</v>
       </c>
@@ -2490,10 +2483,10 @@
         <v>7</v>
       </c>
       <c r="E48" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="49" hidden="1" spans="1:5">
       <c r="A49" t="s">
         <v>77</v>
       </c>
@@ -2507,10 +2500,10 @@
         <v>7</v>
       </c>
       <c r="E49" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="50" hidden="1" spans="1:5">
       <c r="A50" t="s">
         <v>78</v>
       </c>
@@ -2558,7 +2551,7 @@
         <v>80</v>
       </c>
       <c r="E52" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2643,7 +2636,7 @@
         <v>80</v>
       </c>
       <c r="E57" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -2663,7 +2656,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="59" spans="1:5">
+    <row r="59" hidden="1" spans="1:5">
       <c r="A59" t="s">
         <v>88</v>
       </c>
@@ -2680,7 +2673,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="60" spans="1:5">
+    <row r="60" hidden="1" spans="1:5">
       <c r="A60" t="s">
         <v>90</v>
       </c>
@@ -2697,7 +2690,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="61" spans="1:5">
+    <row r="61" hidden="1" spans="1:5">
       <c r="A61" t="s">
         <v>92</v>
       </c>
@@ -2714,9 +2707,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="62" spans="1:5">
+    <row r="62" hidden="1" spans="1:5">
       <c r="A62" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B62">
         <v>4</v>
@@ -2728,10 +2721,10 @@
         <v>80</v>
       </c>
       <c r="E62" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="63" hidden="1" spans="1:5">
       <c r="A63" t="s">
         <v>95</v>
       </c>
@@ -2745,10 +2738,10 @@
         <v>80</v>
       </c>
       <c r="E63" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="64" hidden="1" spans="1:5">
       <c r="A64" t="s">
         <v>97</v>
       </c>
@@ -2765,7 +2758,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" hidden="1" spans="1:5">
       <c r="A65" t="s">
         <v>99</v>
       </c>
@@ -2782,7 +2775,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="66" spans="1:5">
+    <row r="66" hidden="1" spans="1:5">
       <c r="A66" t="s">
         <v>101</v>
       </c>
@@ -2799,7 +2792,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" hidden="1" spans="1:5">
       <c r="A67" t="s">
         <v>103</v>
       </c>
@@ -2807,7 +2800,7 @@
         <v>0</v>
       </c>
       <c r="C67" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D67" t="s">
         <v>80</v>
@@ -2816,7 +2809,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" hidden="1" spans="1:5">
       <c r="A68" t="s">
         <v>104</v>
       </c>
@@ -2824,7 +2817,7 @@
         <v>1</v>
       </c>
       <c r="C68" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D68" t="s">
         <v>80</v>
@@ -2833,7 +2826,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="69" spans="1:5">
+    <row r="69" hidden="1" spans="1:5">
       <c r="A69" t="s">
         <v>105</v>
       </c>
@@ -2841,7 +2834,7 @@
         <v>1</v>
       </c>
       <c r="C69" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D69" t="s">
         <v>80</v>
@@ -2850,7 +2843,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="70" spans="1:5">
+    <row r="70" hidden="1" spans="1:5">
       <c r="A70" t="s">
         <v>106</v>
       </c>
@@ -2858,7 +2851,7 @@
         <v>0</v>
       </c>
       <c r="C70" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D70" t="s">
         <v>80</v>
@@ -2867,7 +2860,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="71" spans="1:5">
+    <row r="71" hidden="1" spans="1:5">
       <c r="A71" t="s">
         <v>107</v>
       </c>
@@ -2875,16 +2868,16 @@
         <v>1</v>
       </c>
       <c r="C71" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D71" t="s">
         <v>80</v>
       </c>
       <c r="E71" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="72" hidden="1" spans="1:5">
       <c r="A72" t="s">
         <v>52</v>
       </c>
@@ -2898,10 +2891,10 @@
         <v>80</v>
       </c>
       <c r="E72" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="73" hidden="1" spans="1:5">
       <c r="A73" t="s">
         <v>50</v>
       </c>
@@ -2909,7 +2902,7 @@
         <v>1</v>
       </c>
       <c r="C73" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D73" t="s">
         <v>80</v>
@@ -2918,7 +2911,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" hidden="1" spans="1:5">
       <c r="A74" t="s">
         <v>109</v>
       </c>
@@ -2926,7 +2919,7 @@
         <v>8</v>
       </c>
       <c r="C74" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D74" t="s">
         <v>80</v>
@@ -2935,7 +2928,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="75" spans="1:5">
+    <row r="75" hidden="1" spans="1:5">
       <c r="A75" t="s">
         <v>110</v>
       </c>
@@ -2943,16 +2936,16 @@
         <v>5</v>
       </c>
       <c r="C75" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D75" t="s">
         <v>80</v>
       </c>
       <c r="E75" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="76" hidden="1" spans="1:5">
       <c r="A76" t="s">
         <v>111</v>
       </c>
@@ -2960,16 +2953,16 @@
         <v>5</v>
       </c>
       <c r="C76" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D76" t="s">
         <v>80</v>
       </c>
       <c r="E76" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="77" hidden="1" spans="1:5">
       <c r="A77" t="s">
         <v>78</v>
       </c>
@@ -2977,7 +2970,7 @@
         <v>2</v>
       </c>
       <c r="C77" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D77" t="s">
         <v>80</v>
@@ -2986,7 +2979,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="78" spans="1:5">
+    <row r="78" hidden="1" spans="1:5">
       <c r="A78" t="s">
         <v>5</v>
       </c>
@@ -3003,7 +2996,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="79" spans="1:5">
+    <row r="79" hidden="1" spans="1:5">
       <c r="A79" t="s">
         <v>112</v>
       </c>
@@ -3020,7 +3013,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="80" spans="1:5">
+    <row r="80" hidden="1" spans="1:5">
       <c r="A80" t="s">
         <v>114</v>
       </c>
@@ -3037,7 +3030,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="81" spans="1:5">
+    <row r="81" hidden="1" spans="1:5">
       <c r="A81" t="s">
         <v>115</v>
       </c>
@@ -3054,7 +3047,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="82" spans="1:5">
+    <row r="82" hidden="1" spans="1:5">
       <c r="A82" t="s">
         <v>116</v>
       </c>
@@ -3068,10 +3061,10 @@
         <v>80</v>
       </c>
       <c r="E82" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="83" hidden="1" spans="1:5">
       <c r="A83" t="s">
         <v>117</v>
       </c>
@@ -3085,10 +3078,10 @@
         <v>80</v>
       </c>
       <c r="E83" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="84" hidden="1" spans="1:5">
       <c r="A84" t="s">
         <v>118</v>
       </c>
@@ -3105,7 +3098,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="85" spans="1:5">
+    <row r="85" hidden="1" spans="1:5">
       <c r="A85" t="s">
         <v>119</v>
       </c>
@@ -3119,10 +3112,10 @@
         <v>80</v>
       </c>
       <c r="E85" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="86" hidden="1" spans="1:5">
       <c r="A86" t="s">
         <v>121</v>
       </c>
@@ -3136,10 +3129,10 @@
         <v>80</v>
       </c>
       <c r="E86" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="87" hidden="1" spans="1:5">
       <c r="A87" t="s">
         <v>122</v>
       </c>
@@ -3153,10 +3146,10 @@
         <v>80</v>
       </c>
       <c r="E87" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="88" hidden="1" spans="1:5">
       <c r="A88" t="s">
         <v>123</v>
       </c>
@@ -3170,10 +3163,10 @@
         <v>80</v>
       </c>
       <c r="E88" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="89" hidden="1" spans="1:5">
       <c r="A89" t="s">
         <v>124</v>
       </c>
@@ -3190,7 +3183,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="90" spans="1:5">
+    <row r="90" hidden="1" spans="1:5">
       <c r="A90" t="s">
         <v>126</v>
       </c>
@@ -3204,10 +3197,10 @@
         <v>80</v>
       </c>
       <c r="E90" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="91" hidden="1" spans="1:5">
       <c r="A91" t="s">
         <v>127</v>
       </c>
@@ -3224,7 +3217,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="92" spans="1:5">
+    <row r="92" hidden="1" spans="1:5">
       <c r="A92" t="s">
         <v>128</v>
       </c>
@@ -3241,7 +3234,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="93" spans="1:5">
+    <row r="93" hidden="1" spans="1:5">
       <c r="A93" t="s">
         <v>129</v>
       </c>
@@ -3258,7 +3251,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="94" spans="1:5">
+    <row r="94" hidden="1" spans="1:5">
       <c r="A94" t="s">
         <v>131</v>
       </c>
@@ -3275,7 +3268,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="95" spans="1:5">
+    <row r="95" hidden="1" spans="1:5">
       <c r="A95" t="s">
         <v>132</v>
       </c>
@@ -3292,7 +3285,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="96" spans="1:5">
+    <row r="96" hidden="1" spans="1:5">
       <c r="A96" t="s">
         <v>133</v>
       </c>
@@ -3309,7 +3302,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="97" spans="1:5">
+    <row r="97" hidden="1" spans="1:5">
       <c r="A97" t="s">
         <v>134</v>
       </c>
@@ -3326,7 +3319,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="98" spans="1:5">
+    <row r="98" hidden="1" spans="1:5">
       <c r="A98" t="s">
         <v>109</v>
       </c>
@@ -3343,7 +3336,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="99" spans="1:5">
+    <row r="99" hidden="1" spans="1:5">
       <c r="A99" t="s">
         <v>110</v>
       </c>
@@ -3357,10 +3350,10 @@
         <v>7</v>
       </c>
       <c r="E99" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="100" hidden="1" spans="1:5">
       <c r="A100" t="s">
         <v>137</v>
       </c>
@@ -3374,10 +3367,10 @@
         <v>7</v>
       </c>
       <c r="E100" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="101" hidden="1" spans="1:5">
       <c r="A101" t="s">
         <v>111</v>
       </c>
@@ -3391,10 +3384,10 @@
         <v>7</v>
       </c>
       <c r="E101" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="102" hidden="1" spans="1:5">
       <c r="A102" t="s">
         <v>119</v>
       </c>
@@ -3408,10 +3401,10 @@
         <v>7</v>
       </c>
       <c r="E102" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="103" hidden="1" spans="1:5">
       <c r="A103" t="s">
         <v>123</v>
       </c>
@@ -3425,10 +3418,10 @@
         <v>7</v>
       </c>
       <c r="E103" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="104" hidden="1" spans="1:5">
       <c r="A104" t="s">
         <v>140</v>
       </c>
@@ -3445,7 +3438,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="105" spans="1:5">
+    <row r="105" hidden="1" spans="1:5">
       <c r="A105" t="s">
         <v>141</v>
       </c>
@@ -3459,10 +3452,10 @@
         <v>7</v>
       </c>
       <c r="E105" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="106" hidden="1" spans="1:5">
       <c r="A106" t="s">
         <v>143</v>
       </c>
@@ -3479,7 +3472,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="107" spans="1:5">
+    <row r="107" hidden="1" spans="1:5">
       <c r="A107" t="s">
         <v>144</v>
       </c>
@@ -3496,7 +3489,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="108" spans="1:5">
+    <row r="108" hidden="1" spans="1:5">
       <c r="A108" t="s">
         <v>146</v>
       </c>
@@ -3513,7 +3506,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="109" spans="1:5">
+    <row r="109" hidden="1" spans="1:5">
       <c r="A109" t="s">
         <v>147</v>
       </c>
@@ -3530,7 +3523,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="110" spans="1:5">
+    <row r="110" hidden="1" spans="1:5">
       <c r="A110" t="s">
         <v>149</v>
       </c>
@@ -3547,24 +3540,24 @@
         <v>8</v>
       </c>
     </row>
-    <row r="111" spans="1:5">
+    <row r="111" hidden="1" spans="1:5">
       <c r="A111" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B111">
         <v>39</v>
       </c>
       <c r="C111" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D111" t="s">
         <v>7</v>
       </c>
       <c r="E111" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="112" hidden="1" spans="1:5">
       <c r="A112" t="s">
         <v>52</v>
       </c>
@@ -3578,27 +3571,27 @@
         <v>7</v>
       </c>
       <c r="E112" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="113" hidden="1" spans="1:5">
       <c r="A113" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B113">
         <v>39</v>
       </c>
       <c r="C113" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D113" t="s">
         <v>7</v>
       </c>
       <c r="E113" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="114" hidden="1" spans="1:5">
       <c r="A114" t="s">
         <v>53</v>
       </c>
@@ -3612,10 +3605,10 @@
         <v>7</v>
       </c>
       <c r="E114" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="115" hidden="1" spans="1:5">
       <c r="A115" t="s">
         <v>151</v>
       </c>
@@ -3632,7 +3625,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="116" spans="1:5">
+    <row r="116" hidden="1" spans="1:5">
       <c r="A116" t="s">
         <v>153</v>
       </c>
@@ -3649,7 +3642,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="117" spans="1:5">
+    <row r="117" hidden="1" spans="1:5">
       <c r="A117" t="s">
         <v>64</v>
       </c>
@@ -3666,7 +3659,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="118" spans="1:5">
+    <row r="118" hidden="1" spans="1:5">
       <c r="A118" t="s">
         <v>154</v>
       </c>
@@ -3683,7 +3676,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="119" spans="1:5">
+    <row r="119" hidden="1" spans="1:5">
       <c r="A119" t="s">
         <v>155</v>
       </c>
@@ -3697,10 +3690,10 @@
         <v>7</v>
       </c>
       <c r="E119" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="120" hidden="1" spans="1:5">
       <c r="A120" t="s">
         <v>156</v>
       </c>
@@ -3714,10 +3707,10 @@
         <v>7</v>
       </c>
       <c r="E120" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="121" hidden="1" spans="1:5">
       <c r="A121" t="s">
         <v>157</v>
       </c>
@@ -3734,7 +3727,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="122" spans="1:5">
+    <row r="122" hidden="1" spans="1:5">
       <c r="A122" t="s">
         <v>159</v>
       </c>
@@ -3751,7 +3744,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="123" spans="1:5">
+    <row r="123" hidden="1" spans="1:5">
       <c r="A123" t="s">
         <v>160</v>
       </c>
@@ -3768,7 +3761,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="124" spans="1:5">
+    <row r="124" hidden="1" spans="1:5">
       <c r="A124" t="s">
         <v>161</v>
       </c>
@@ -3785,7 +3778,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="125" spans="1:5">
+    <row r="125" hidden="1" spans="1:5">
       <c r="A125" t="s">
         <v>162</v>
       </c>
@@ -3799,10 +3792,10 @@
         <v>7</v>
       </c>
       <c r="E125" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="126" hidden="1" spans="1:5">
       <c r="A126" t="s">
         <v>164</v>
       </c>
@@ -3819,7 +3812,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="127" spans="1:5">
+    <row r="127" hidden="1" spans="1:5">
       <c r="A127" t="s">
         <v>165</v>
       </c>
@@ -3836,7 +3829,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="128" spans="1:5">
+    <row r="128" hidden="1" spans="1:5">
       <c r="A128" t="s">
         <v>166</v>
       </c>
@@ -3853,7 +3846,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="129" spans="1:5">
+    <row r="129" hidden="1" spans="1:5">
       <c r="A129" t="s">
         <v>167</v>
       </c>
@@ -3870,7 +3863,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="130" spans="1:5">
+    <row r="130" hidden="1" spans="1:5">
       <c r="A130" t="s">
         <v>168</v>
       </c>
@@ -3887,7 +3880,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="131" spans="1:5">
+    <row r="131" hidden="1" spans="1:5">
       <c r="A131" t="s">
         <v>169</v>
       </c>
@@ -3904,7 +3897,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="132" spans="1:5">
+    <row r="132" hidden="1" spans="1:5">
       <c r="A132" t="s">
         <v>171</v>
       </c>
@@ -3921,7 +3914,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="133" spans="1:5">
+    <row r="133" hidden="1" spans="1:5">
       <c r="A133" t="s">
         <v>173</v>
       </c>
@@ -3938,7 +3931,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="134" spans="1:5">
+    <row r="134" hidden="1" spans="1:5">
       <c r="A134" t="s">
         <v>174</v>
       </c>
@@ -3952,10 +3945,10 @@
         <v>7</v>
       </c>
       <c r="E134" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="135" hidden="1" spans="1:5">
       <c r="A135" t="s">
         <v>175</v>
       </c>
@@ -3972,7 +3965,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="136" spans="1:5">
+    <row r="136" hidden="1" spans="1:5">
       <c r="A136" t="s">
         <v>177</v>
       </c>
@@ -3986,10 +3979,10 @@
         <v>7</v>
       </c>
       <c r="E136" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="137" hidden="1" spans="1:5">
       <c r="A137" t="s">
         <v>178</v>
       </c>
@@ -4003,10 +3996,10 @@
         <v>7</v>
       </c>
       <c r="E137" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="138" hidden="1" spans="1:5">
       <c r="A138" t="s">
         <v>179</v>
       </c>
@@ -4020,10 +4013,10 @@
         <v>7</v>
       </c>
       <c r="E138" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="139" hidden="1" spans="1:5">
       <c r="A139" t="s">
         <v>77</v>
       </c>
@@ -4037,18 +4030,18 @@
         <v>7</v>
       </c>
       <c r="E139" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="140" hidden="1" spans="1:5">
       <c r="A140" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B140">
         <v>13</v>
       </c>
       <c r="C140" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D140" t="s">
         <v>7</v>
@@ -4057,7 +4050,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="141" spans="1:5">
+    <row r="141" hidden="1" spans="1:5">
       <c r="A141" t="s">
         <v>180</v>
       </c>
@@ -4071,10 +4064,10 @@
         <v>7</v>
       </c>
       <c r="E141" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="142" hidden="1" spans="1:5">
       <c r="A142" t="s">
         <v>78</v>
       </c>
@@ -4091,7 +4084,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="143" spans="1:5">
+    <row r="143" hidden="1" spans="1:5">
       <c r="A143" t="s">
         <v>50</v>
       </c>
@@ -4108,7 +4101,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="144" spans="1:5">
+    <row r="144" hidden="1" spans="1:5">
       <c r="A144" t="s">
         <v>58</v>
       </c>
@@ -4125,7 +4118,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="145" spans="1:5">
+    <row r="145" hidden="1" spans="1:5">
       <c r="A145" t="s">
         <v>141</v>
       </c>
@@ -4139,10 +4132,10 @@
         <v>80</v>
       </c>
       <c r="E145" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="146" spans="1:5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="146" hidden="1" spans="1:5">
       <c r="A146" t="s">
         <v>181</v>
       </c>
@@ -4156,10 +4149,10 @@
         <v>80</v>
       </c>
       <c r="E146" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="147" spans="1:5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="147" hidden="1" spans="1:5">
       <c r="A147" t="s">
         <v>122</v>
       </c>
@@ -4173,10 +4166,10 @@
         <v>80</v>
       </c>
       <c r="E147" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="148" spans="1:5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="148" hidden="1" spans="1:5">
       <c r="A148" t="s">
         <v>119</v>
       </c>
@@ -4190,10 +4183,10 @@
         <v>80</v>
       </c>
       <c r="E148" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="149" spans="1:5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="149" hidden="1" spans="1:5">
       <c r="A149" t="s">
         <v>123</v>
       </c>
@@ -4207,10 +4200,10 @@
         <v>80</v>
       </c>
       <c r="E149" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="150" spans="1:5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="150" hidden="1" spans="1:5">
       <c r="A150" t="s">
         <v>101</v>
       </c>
@@ -4227,7 +4220,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="151" spans="1:5">
+    <row r="151" hidden="1" spans="1:5">
       <c r="A151" t="s">
         <v>182</v>
       </c>
@@ -4244,7 +4237,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="152" spans="1:5">
+    <row r="152" hidden="1" spans="1:5">
       <c r="A152" t="s">
         <v>183</v>
       </c>
@@ -4258,10 +4251,10 @@
         <v>80</v>
       </c>
       <c r="E152" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="153" spans="1:5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="153" hidden="1" spans="1:5">
       <c r="A153" t="s">
         <v>157</v>
       </c>
@@ -4278,7 +4271,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="154" spans="1:5">
+    <row r="154" hidden="1" spans="1:5">
       <c r="A154" t="s">
         <v>184</v>
       </c>
@@ -4295,7 +4288,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="155" spans="1:5">
+    <row r="155" hidden="1" spans="1:5">
       <c r="A155" t="s">
         <v>127</v>
       </c>
@@ -4312,7 +4305,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="156" spans="1:5">
+    <row r="156" hidden="1" spans="1:5">
       <c r="A156" t="s">
         <v>185</v>
       </c>
@@ -4329,7 +4322,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="157" spans="1:5">
+    <row r="157" hidden="1" spans="1:5">
       <c r="A157" t="s">
         <v>186</v>
       </c>
@@ -4343,10 +4336,10 @@
         <v>80</v>
       </c>
       <c r="E157" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="158" spans="1:5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="158" hidden="1" spans="1:5">
       <c r="A158" t="s">
         <v>149</v>
       </c>
@@ -4363,7 +4356,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="159" spans="1:5">
+    <row r="159" hidden="1" spans="1:5">
       <c r="A159" t="s">
         <v>187</v>
       </c>
@@ -4377,10 +4370,10 @@
         <v>80</v>
       </c>
       <c r="E159" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="160" spans="1:5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="160" hidden="1" spans="1:5">
       <c r="A160" t="s">
         <v>188</v>
       </c>
@@ -4394,10 +4387,10 @@
         <v>80</v>
       </c>
       <c r="E160" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="161" spans="1:5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="161" hidden="1" spans="1:5">
       <c r="A161" t="s">
         <v>189</v>
       </c>
@@ -4414,7 +4407,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="162" spans="1:5">
+    <row r="162" hidden="1" spans="1:5">
       <c r="A162" t="s">
         <v>190</v>
       </c>
@@ -4428,10 +4421,10 @@
         <v>80</v>
       </c>
       <c r="E162" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="163" spans="1:5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="163" hidden="1" spans="1:5">
       <c r="A163" t="s">
         <v>191</v>
       </c>
@@ -4445,10 +4438,10 @@
         <v>80</v>
       </c>
       <c r="E163" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="164" spans="1:5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="164" hidden="1" spans="1:5">
       <c r="A164" t="s">
         <v>192</v>
       </c>
@@ -4465,7 +4458,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="165" spans="1:5">
+    <row r="165" hidden="1" spans="1:5">
       <c r="A165" t="s">
         <v>193</v>
       </c>
@@ -4479,10 +4472,10 @@
         <v>80</v>
       </c>
       <c r="E165" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="166" spans="1:5">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="166" hidden="1" spans="1:5">
       <c r="A166" t="s">
         <v>140</v>
       </c>
@@ -4499,7 +4492,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="167" spans="1:5">
+    <row r="167" hidden="1" spans="1:5">
       <c r="A167" t="s">
         <v>126</v>
       </c>
@@ -4513,10 +4506,10 @@
         <v>80</v>
       </c>
       <c r="E167" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="168" spans="1:5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="168" hidden="1" spans="1:5">
       <c r="A168" t="s">
         <v>131</v>
       </c>
@@ -4533,7 +4526,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="169" spans="1:5">
+    <row r="169" hidden="1" spans="1:5">
       <c r="A169" t="s">
         <v>194</v>
       </c>
@@ -4547,10 +4540,10 @@
         <v>80</v>
       </c>
       <c r="E169" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="170" spans="1:5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="170" hidden="1" spans="1:5">
       <c r="A170" t="s">
         <v>196</v>
       </c>
@@ -4567,7 +4560,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="171" spans="1:5">
+    <row r="171" hidden="1" spans="1:5">
       <c r="A171" t="s">
         <v>166</v>
       </c>
@@ -4584,7 +4577,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="172" spans="1:5">
+    <row r="172" hidden="1" spans="1:5">
       <c r="A172" t="s">
         <v>198</v>
       </c>
@@ -4601,7 +4594,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="173" spans="1:5">
+    <row r="173" hidden="1" spans="1:5">
       <c r="A173" t="s">
         <v>199</v>
       </c>
@@ -4615,10 +4608,10 @@
         <v>80</v>
       </c>
       <c r="E173" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="174" spans="1:5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="174" hidden="1" spans="1:5">
       <c r="A174" t="s">
         <v>200</v>
       </c>
@@ -4635,7 +4628,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="175" spans="1:5">
+    <row r="175" hidden="1" spans="1:5">
       <c r="A175" t="s">
         <v>201</v>
       </c>
@@ -4652,7 +4645,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="176" spans="1:5">
+    <row r="176" hidden="1" spans="1:5">
       <c r="A176" t="s">
         <v>116</v>
       </c>
@@ -4666,10 +4659,10 @@
         <v>80</v>
       </c>
       <c r="E176" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="177" spans="1:5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="177" hidden="1" spans="1:5">
       <c r="A177" t="s">
         <v>117</v>
       </c>
@@ -4683,10 +4676,10 @@
         <v>80</v>
       </c>
       <c r="E177" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="178" spans="1:5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="178" hidden="1" spans="1:5">
       <c r="A178" t="s">
         <v>202</v>
       </c>
@@ -4700,10 +4693,10 @@
         <v>80</v>
       </c>
       <c r="E178" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="179" spans="1:5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="179" hidden="1" spans="1:5">
       <c r="A179" t="s">
         <v>203</v>
       </c>
@@ -4720,7 +4713,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="180" spans="1:5">
+    <row r="180" hidden="1" spans="1:5">
       <c r="A180" t="s">
         <v>204</v>
       </c>
@@ -4737,7 +4730,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="181" spans="1:5">
+    <row r="181" hidden="1" spans="1:5">
       <c r="A181" t="s">
         <v>205</v>
       </c>
@@ -4754,7 +4747,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="182" spans="1:5">
+    <row r="182" hidden="1" spans="1:5">
       <c r="A182" t="s">
         <v>109</v>
       </c>
@@ -4762,7 +4755,7 @@
         <v>8</v>
       </c>
       <c r="C182" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D182" t="s">
         <v>80</v>
@@ -4771,7 +4764,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="183" spans="1:5">
+    <row r="183" hidden="1" spans="1:5">
       <c r="A183" t="s">
         <v>206</v>
       </c>
@@ -4788,7 +4781,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="184" spans="1:5">
+    <row r="184" hidden="1" spans="1:5">
       <c r="A184" t="s">
         <v>207</v>
       </c>
@@ -4802,10 +4795,10 @@
         <v>80</v>
       </c>
       <c r="E184" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="185" spans="1:5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="185" hidden="1" spans="1:5">
       <c r="A185" t="s">
         <v>208</v>
       </c>
@@ -4819,10 +4812,10 @@
         <v>80</v>
       </c>
       <c r="E185" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="186" spans="1:5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="186" hidden="1" spans="1:5">
       <c r="A186" t="s">
         <v>209</v>
       </c>
@@ -4839,7 +4832,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="187" spans="1:5">
+    <row r="187" hidden="1" spans="1:5">
       <c r="A187" t="s">
         <v>210</v>
       </c>
@@ -4856,7 +4849,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="188" spans="1:5">
+    <row r="188" hidden="1" spans="1:5">
       <c r="A188" t="s">
         <v>211</v>
       </c>
@@ -4873,7 +4866,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="189" spans="1:5">
+    <row r="189" hidden="1" spans="1:5">
       <c r="A189" t="s">
         <v>175</v>
       </c>
@@ -4892,10 +4885,15 @@
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:E189" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="Breakout"/>
+      </filters>
+    </filterColumn>
     <extLst/>
   </autoFilter>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E30 E31 E38 E39 E74 E107 E115 E116 E121 E144 E161 E171 E174 E187 E1:E29 E32:E33 E34:E37 E40:E41 E42:E43 E44:E46 E47:E73 E75:E95 E96:E98 E99:E106 E108:E114 E117:E118 E119:E120 E122:E127 E128:E129 E130:E143 E145:E152 E153:E154 E155:E160 E162:E170 E172:E173 E175:E178 E179:E182 E183:E186 E188:E1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E$1:E$1048576">
       <formula1>"概念了解,相关信息,周边项目,安装部署,模型配置,渠道接入,技能扩展,使用教程,竞品对比,其他未知"</formula1>
     </dataValidation>
   </dataValidations>
